--- a/data/processed/pkm2026/all_mandates.xlsx
+++ b/data/processed/pkm2026/all_mandates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,57 +481,53 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/590)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.1.json</t>
+          <t>A_80_590.json</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>UNDOF</t>
+          <t>MINUSMA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>United Nations Disengagement Observer Force</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Add.1</t>
-        </is>
-      </c>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Disengagement Observer Force</t>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate performance</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The mandate of UNDOF was established by the Security Council in its resolution 350 (1974) and was renewed most recently in its resolution 2811 (2025), by which it was extended until 30 June 2026.</t>
+          <t>The mandate of MINUSMA was established by the Security Council in its resolution 2100 (2013) and extended in subsequent resolutions of the Council.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/350(1974)</t>
+          <t>https://docs.un.org/en/S/RES/2100(2013)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>350 (1974)</t>
+          <t>2100 (2013)</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>S/RES/350(1974)</t>
+          <t>S/RES/2100(2013)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -543,57 +539,53 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/590)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.1.json</t>
+          <t>A_80_590.json</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>UNDOF</t>
+          <t>MINUSMA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>United Nations Disengagement Observer Force</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Add.1</t>
-        </is>
-      </c>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Disengagement Observer Force</t>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate performance</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The mandate of UNDOF was established by the Security Council in its resolution 350 (1974) and was renewed most recently in its resolution 2811 (2025), by which it was extended until 30 June 2026.</t>
+          <t>The mandate for the performance reporting period was provided by the Council in its resolution 2690 (2023).</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2811(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2690(2023)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2811 (2025)</t>
+          <t>2690 (2023)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>S/RES/2811(2025)</t>
+          <t>S/RES/2690(2023)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -605,57 +597,53 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/590)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.2.json</t>
+          <t>A_80_590.json</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UNFICYP</t>
+          <t>MINUSMA</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>United Nations Peacekeeping Force in Cyprus</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Add.2</t>
-        </is>
-      </c>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate performance</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>UNFICYP was established by the Security Council in its resolution 186 (1964), and its mandate was extended most recently, until 31 January 2027, pursuant to resolution 2815 (2026).</t>
+          <t>The Security Council, in paragraph 1 of resolution 2690 (2023), decided to terminate the mandate of MINUSMA under resolution 2640 (2022) as from 30 June 2023.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/186(1964)</t>
+          <t>https://docs.un.org/en/S/RES/2690(2023)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>186 (1964)</t>
+          <t>2690 (2023)</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>S/RES/186(1964)</t>
+          <t>S/RES/2690(2023)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -667,57 +655,53 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/590)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.2.json</t>
+          <t>A_80_590.json</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>UNFICYP</t>
+          <t>MINUSMA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>United Nations Peacekeeping Force in Cyprus</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Add.2</t>
-        </is>
-      </c>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate performance</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>UNFICYP was established by the Security Council in its resolution 186 (1964), and its mandate was extended most recently, until 31 January 2027, pursuant to resolution 2815 (2026).</t>
+          <t>The Security Council, in paragraph 1 of resolution 2690 (2023), decided to terminate the mandate of MINUSMA under resolution 2640 (2022) as from 30 June 2023.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2815(2026)</t>
+          <t>https://docs.un.org/en/S/RES/2640(2022)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2815 (2026)</t>
+          <t>2640 (2022)</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>S/RES/2815(2026)</t>
+          <t>S/RES/2640(2022)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -729,57 +713,53 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/596)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.3.json</t>
+          <t>A_80_596.json</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MINURSO</t>
+          <t>UNDOF</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>United Nations Mission for the Referendum in Western Sahara</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Add.3</t>
-        </is>
-      </c>
+          <t>United Nations Disengagement Observer Force</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Disengagement Observer Force</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The mandate of MINURSO was established by the Security Council in its resolution 690 (1991) and extended most recently, until 31 October 2026, in its resolution 2797 (2025).</t>
+          <t>The mandate of the United Nations Disengagement Observation Force (UNDOF) was established by the Security Council in its resolution 350 (1974).</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/690(1991)</t>
+          <t>https://docs.un.org/en/S/RES/350(1974)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>690 (1991)</t>
+          <t>350 (1974)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>S/RES/690(1991)</t>
+          <t>S/RES/350(1974)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -791,57 +771,53 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/596)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.3.json</t>
+          <t>A_80_596.json</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MINURSO</t>
+          <t>UNDOF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>United Nations Mission for the Referendum in Western Sahara</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Add.3</t>
-        </is>
-      </c>
+          <t>United Nations Disengagement Observer Force</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Disengagement Observer Force</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The mandate of MINURSO was established by the Security Council in its resolution 690 (1991) and extended most recently, until 31 October 2026, in its resolution 2797 (2025).</t>
+          <t>The mandate for the performance period was provided in its resolutions 2737 (2024) and 2766 (2024).</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2797(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2737(2024)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2797 (2025)</t>
+          <t>2737 (2024)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>S/RES/2797(2025)</t>
+          <t>S/RES/2737(2024)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -853,181 +829,169 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/596)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.4.json</t>
+          <t>A_80_596.json</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>RSCE</t>
+          <t>UNDOF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Regional Service Centre in Entebbe</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Add.4</t>
-        </is>
-      </c>
+          <t>United Nations Disengagement Observer Force</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Disengagement Observer Force</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>The Regional Service Centre in Entebbe was established in July 2010, following the adoption by the General Assembly of its resolution 64/269, as a shared service centre for missions in the region under the global field support strategy.</t>
+          <t>The mandate for the performance period was provided in its resolutions 2737 (2024) and 2766 (2024).</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/A/RES/64/269</t>
+          <t>https://docs.un.org/en/S/RES/2766(2024)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>64/269</t>
+          <t>2766 (2024)</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>A/RES/64/269</t>
+          <t>S/RES/2766(2024)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>General Assembly resolutions</t>
+          <t>Security Council resolutions</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/596)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.4.json</t>
+          <t>A_80_596.json</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RSCE</t>
+          <t>UNDOF</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Regional Service Centre in Entebbe</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Add.4</t>
-        </is>
-      </c>
+          <t>United Nations Disengagement Observer Force</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Disengagement Observer Force</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>By its resolution 78/294, the Assembly expanded the mandate of RSCE to provide additional services to other entities, including the African Union.</t>
+          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2811 (2025), by which it extended the Force’s mandate until 30 June 2026.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/A/RES/78/294</t>
+          <t>https://docs.un.org/en/S/RES/2811(2025)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78/294</t>
+          <t>2811 (2025)</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>A/RES/78/294</t>
+          <t>S/RES/2811(2025)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>General Assembly resolutions</t>
+          <t>Security Council resolutions</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/600)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.6.json</t>
+          <t>A_80_600.json</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UNMIK</t>
+          <t>MINURSO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>United Nations Interim Administration Mission in Kosovo</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Add.6</t>
-        </is>
-      </c>
+          <t>United Nations Mission for the Referendum in Western Sahara</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Interim Administration Mission in Kosovo</t>
+          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The mandate of UNMIK was established by the Security Council in its resolution 1244 (1999).</t>
+          <t>The mandate of the United Nations Mission for the Referendum in Western Sahara (MINURSO) was established by the Security Council in its resolution 690 (1991).</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1244(1999)</t>
+          <t>https://docs.un.org/en/S/RES/690(1991)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1244 (1999)</t>
+          <t>690 (1991)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>S/RES/1244(1999)</t>
+          <t>S/RES/690(1991)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1039,57 +1003,53 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/600)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.7.json</t>
+          <t>A_80_600.json</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNSOS</t>
+          <t>MINURSO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Somalia</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Add.7</t>
-        </is>
-      </c>
+          <t>United Nations Mission for the Referendum in Western Sahara</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>The mandate of UNSOS was established by the Security Council in resolution 1863 (2009) and was most recently extended until 31 December 2026 in Council resolution 2809 (2025).</t>
+          <t>The mandate for the performance period was provided in its resolutions 2703 (2023) and 2756 (2024).</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1863(2009)</t>
+          <t>https://docs.un.org/en/S/RES/2703(2023)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1863 (2009)</t>
+          <t>2703 (2023)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>S/RES/1863(2009)</t>
+          <t>S/RES/2703(2023)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1101,57 +1061,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/600)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.7.json</t>
+          <t>A_80_600.json</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNSOS</t>
+          <t>MINURSO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Somalia</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Add.7</t>
-        </is>
-      </c>
+          <t>United Nations Mission for the Referendum in Western Sahara</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>The mandate of UNSOS was established by the Security Council in resolution 1863 (2009) and was most recently extended until 31 December 2026 in Council resolution 2809 (2025).</t>
+          <t>The mandate for the performance period was provided in its resolutions 2703 (2023) and 2756 (2024).</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2809(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2756(2024)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2809 (2025)</t>
+          <t>2756 (2024)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>S/RES/2809(2025)</t>
+          <t>S/RES/2756(2024)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1163,57 +1119,53 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/600)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.7.json</t>
+          <t>A_80_600.json</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UNSOS</t>
+          <t>MINURSO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Somalia</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Add.7</t>
-        </is>
-      </c>
+          <t>United Nations Mission for the Referendum in Western Sahara</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>For the 2026/27 period, UNSOS support will continue to be aligned with the phased implementation of the AUSSOM strategic concept of operations (2024) (see Security Council resolution 2767 (2024)).</t>
+          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2797 (2025), by which it extended the mandate until 31 October 2026.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2767(2024)</t>
+          <t>https://docs.un.org/en/S/RES/2797(2025)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2767 (2024)</t>
+          <t>2797 (2025)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>S/RES/2767(2024)</t>
+          <t>S/RES/2797(2025)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1225,615 +1177,543 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/600)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.7.json</t>
+          <t>A_80_600.json</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>UNSOS</t>
+          <t>MINURSO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Somalia</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Add.7</t>
-        </is>
-      </c>
+          <t>United Nations Mission for the Referendum in Western Sahara</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>The Advisory Committee notes that phase 1 of the approved concept of operations planned for the realignment of troops and the transfer of locations to Somali security forces and recalls that the budget for UNSOS for 2024/25 was proposed and approved on the basis of 10,626 ATMIS personnel, in accordance with Security Council resolution 2710 (2023), but 12,626 were retained throughout the same period, pursuant to resolution 2741 (2024).</t>
+          <t>During the 2024/25 period, the Office of Internal Oversight Services conducted an evaluation of MINURSO (IED-24-020) in accordance with General Assembly resolution 48/218 B.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2710(2023)</t>
+          <t>https://docs.un.org/en/A/RES/48/218B</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2710 (2023)</t>
+          <t>48/218</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>S/RES/2710(2023)</t>
+          <t>A/RES/48/218B</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/605)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.7.json</t>
+          <t>A_80_605.json</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>UNSOS</t>
+          <t>UNLB</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Somalia</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Add.7</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
-        </is>
-      </c>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>The Advisory Committee notes that phase 1 of the approved concept of operations planned for the realignment of troops and the transfer of locations to Somali security forces and recalls that the budget for UNSOS for 2024/25 was proposed and approved on the basis of 10,626 ATMIS personnel, in accordance with Security Council resolution 2710 (2023), but 12,626 were retained throughout the same period, pursuant to resolution 2741 (2024).</t>
+          <t>In its resolution 49/233 A of 23 December 1994, the General Assembly welcomed the establishment of the first permanent United Nations logistics base in Brindisi, Italy, to support peacekeeping operations.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2741(2024)</t>
+          <t>https://docs.un.org/en/A/RES/49/233</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2741 (2024)</t>
+          <t>49/233</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>S/RES/2741(2024)</t>
+          <t>A/RES/49/233</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/605)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.7.json</t>
+          <t>A_80_605.json</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNSOS</t>
+          <t>UNLB</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Somalia</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Add.7</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
-        </is>
-      </c>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Subsequently, in paragraph 21 of its resolution 2767 (2024), the Council adjusted the authorized ceiling to 11,826 uniformed personnel beginning from 1 July 2025, which resulted in movements of contingents during the current budget period, including the repatriation of one formed police unit and 470 defence forces personnel, together with associated contingent-owned equipment.</t>
+          <t>Subsequently, in its resolution 63/262 of 24 December 2008, the General Assembly approved the establishment of site B, in Valencia, Spain, as a secondary active telecommunications and information technology facility to strengthen operational resilience and ensure business continuity in support of peacekeeping activities.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2767(2024)</t>
+          <t>https://docs.un.org/en/A/RES/63/262</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2767 (2024)</t>
+          <t>63/262</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>S/RES/2767(2024)</t>
+          <t>A/RES/63/262</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/605)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.7.json</t>
+          <t>A_80_605.json</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UNSOS</t>
+          <t>UNLB</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Somalia</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Add.7</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
-        </is>
-      </c>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>UNSOS will continue to provide mandated logistics support to the Somali security forces engaged in joint or coordinated operations with AUSSOM through the United Nations trust fund established by Security Council resolution 2124 (2013) (ibid.</t>
+          <t>As part of the Department of Operational Support, UNLB is mandated to serve all field missions, all Secretariat entities, and United Nations system entities, as well as to cooperate in developing broader cooperation with regional organizations, in alignment with the Department’s mandate under the guidance of the Office of Supply Chain Management, pursuant to General Assembly resolution 72/266 B on shifting the management paradigm in the United Nations and the recommendation of the Advisory Committee (A/78/744/Add.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2124(2013)</t>
+          <t>https://docs.un.org/en/A/RES/72/266B</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2124 (2013)</t>
+          <t>72/266</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>S/RES/2124(2013)</t>
+          <t>A/RES/72/266B</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/605)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.7.json</t>
+          <t>A_80_605.json</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>UNSOS</t>
+          <t>UNLB</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Somalia</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Add.7</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
-        </is>
-      </c>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Following the anticipated closure of UNTMIS by 31 October 2026 in accordance with Security Council resolution 2753 (2024), UNSOS will implement the UNTMIS mission support transition plan, including the reduction of its physical footprint, environmental cleanup, asset disposal and administrative support (A/80/628, para.</t>
+          <t>44) endorsed by the Assembly in its resolution 78/295.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2753(2024)</t>
+          <t>https://docs.un.org/en/A/RES/78/295</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2753 (2024)</t>
+          <t>78/295</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>S/RES/2753(2024)</t>
+          <t>A/RES/78/295</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/605)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.7.json</t>
+          <t>A_80_605.json</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UNSOS</t>
+          <t>UNLB</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Somalia</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Add.7</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
-        </is>
-      </c>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>UNSOS will also be responsible for the implementation of the human rights due diligence policy in Somalia, pursuant to Security Council resolution 2809 (2025), which has been conducted by UNTMIS to date (A/80/628, para.</t>
+          <t>The budgets of tenant units and the regional aviation safety office were transferred to their respective parent offices under the support account for peacekeeping operations, effective from the 2025/26 period, as approved by the General Assembly in its resolution 79/300.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2809(2025)</t>
+          <t>https://docs.un.org/en/A/RES/79/300</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2809 (2025)</t>
+          <t>79/300</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>S/RES/2809(2025)</t>
+          <t>A/RES/79/300</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/605)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.7.json</t>
+          <t>A_80_605.json</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UNSOS</t>
+          <t>UNLB</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Somalia</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Add.7</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
-        </is>
-      </c>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Upon enquiry, the Advisory Committee was informed that the independent strategic review pursuant to Security Council resolution 2767 (2024), conducted in early 2025, identified structural efficiencies amounting to at least $43.</t>
+          <t>31) endorsed by the General Assembly in its resolution 79/300.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2767(2024)</t>
+          <t>https://docs.un.org/en/A/RES/79/300</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2767 (2024)</t>
+          <t>79/300</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>S/RES/2767(2024)</t>
+          <t>A/RES/79/300</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/605)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.8.json</t>
+          <t>A_80_605.json</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UNSOH</t>
+          <t>UNLB</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Haiti</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Add.8</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Financing of the United Nations Support Office in Haiti</t>
-        </is>
-      </c>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The Security Council, by its resolution 2793 (2025) of 30 September 2025, acting under Chapter VII of the Charter of the United Nations, authorized Member States to transition the Multinational Security Support Mission to the Gang Suppression Force, with an authorized ceiling of 5,550 personnel (5,500 uniformed military and police personnel and 50 civilians).</t>
+          <t>), endorsed by the General Assembly in its resolution 78/295, planning assumptions for strategic deployment stocks had been revised.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
+          <t>https://docs.un.org/en/A/RES/78/295</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2793 (2025)</t>
+          <t>78/295</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>S/RES/2793(2025)</t>
+          <t>A/RES/78/295</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/605)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.8.json</t>
+          <t>A_80_605.json</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UNSOH</t>
+          <t>UNLB</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Haiti</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Add.8</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Financing of the United Nations Support Office in Haiti</t>
-        </is>
-      </c>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>In its resolution 2793 (2025), the Security Council also indicates that the Standing Group of Partners for the Gang Suppression Force is responsible for the selection of the special representative for the Force, who was appointed in December 2025, to provide strategic representation and coordination and also of the Force Commander of the Force, to be responsible for operational command and day-to-day operational decision-making.</t>
+          <t>In 2026/27, the Base will enhance collaboration with regional organizations, in particular the African Union, to improve operational synergies, innovation and joint capabilities in line with General Assembly resolution 79/329.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
+          <t>https://docs.un.org/en/A/RES/79/329</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2793 (2025)</t>
+          <t>79/329</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>S/RES/2793(2025)</t>
+          <t>A/RES/79/329</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/607)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.8.json</t>
+          <t>A_80_607.json</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UNSOH</t>
+          <t>UNFICYP</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Haiti</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>Add.8</t>
-        </is>
-      </c>
+          <t>United Nations Peacekeeping Force in Cyprus</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Support Office in Haiti</t>
+          <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>In its resolution 2793 (2025), the Security Council requested the Secretary-General to ensure strong coordination and cooperation among all actors in the United Nations system in order to prevent duplication of effort and to maximize the leveraging of existing resources, and stressed that the Head of UNSOH should have separate quantifiable compacts with the Head of BINUH for the delivery of support to BINUH and with the special representative for the Gang Suppression Force.</t>
+          <t>The mandate of UNFICYP was established by the Security Council in its resolution 186 (1964).</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
+          <t>https://docs.un.org/en/S/RES/186(1964)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2793 (2025)</t>
+          <t>186 (1964)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>S/RES/2793(2025)</t>
+          <t>S/RES/186(1964)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1845,57 +1725,53 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/607)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.9.json</t>
+          <t>A_80_607.json</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MINUSCA</t>
+          <t>UNFICYP</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Add.9</t>
-        </is>
-      </c>
+          <t>United Nations Peacekeeping Force in Cyprus</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+          <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>MINUSCA was established by the Security Council in its resolution 2149 (2014), and its mandate was most recently extended until 15 November 2026 in Council resolution 2800 (2025).</t>
+          <t>The mandate for the performance period was provided in its resolutions 2674 (2023) and 2723 (2024).</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2149(2014)</t>
+          <t>https://docs.un.org/en/S/RES/2674(2023)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2149 (2014)</t>
+          <t>2674 (2023)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>S/RES/2149(2014)</t>
+          <t>S/RES/2674(2023)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1907,57 +1783,53 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/607)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.9.json</t>
+          <t>A_80_607.json</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MINUSCA</t>
+          <t>UNFICYP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Add.9</t>
-        </is>
-      </c>
+          <t>United Nations Peacekeeping Force in Cyprus</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+          <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>MINUSCA was established by the Security Council in its resolution 2149 (2014), and its mandate was most recently extended until 15 November 2026 in Council resolution 2800 (2025).</t>
+          <t>The mandate for the performance period was provided in its resolutions 2674 (2023) and 2723 (2024).</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2800(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2723(2024)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2800 (2025)</t>
+          <t>2723 (2024)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>S/RES/2800(2025)</t>
+          <t>S/RES/2723(2024)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1969,57 +1841,53 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/607)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.10.json</t>
+          <t>A_80_607.json</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>UNISFA</t>
+          <t>UNFICYP</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>United Nations Interim Security Force for Abyei</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Add.10</t>
-        </is>
-      </c>
+          <t>United Nations Peacekeeping Force in Cyprus</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Interim Security Force for Abyei</t>
+          <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>The mandate of UNISFA was established by the Security Council in its resolution 1990 (2011) and most recently extended by the Council in its resolution 2802 (2025), until 15 November 2026.</t>
+          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2815 (2026), by which it extended the mandate until 31 January 2027.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1990(2011)</t>
+          <t>https://docs.un.org/en/S/RES/2815(2026)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1990 (2011)</t>
+          <t>2815 (2026)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>S/RES/1990(2011)</t>
+          <t>S/RES/2815(2026)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2031,57 +1899,53 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/607)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.10.json</t>
+          <t>A_80_607.json</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UNISFA</t>
+          <t>UNFICYP</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>United Nations Interim Security Force for Abyei</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Add.10</t>
-        </is>
-      </c>
+          <t>United Nations Peacekeeping Force in Cyprus</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Interim Security Force for Abyei</t>
+          <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>The mandate of UNISFA was established by the Security Council in its resolution 1990 (2011) and most recently extended by the Council in its resolution 2802 (2025), until 15 November 2026.</t>
+          <t>The Security Council, in its resolution 2771 (2025), urged the leaders to increase their support to, and ensure a meaningful role for, civil society engagement in peace efforts, in particular strengthening the participation of women’s organizations and young people in the process.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2802(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2771(2025)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2802 (2025)</t>
+          <t>2771 (2025)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>S/RES/2802(2025)</t>
+          <t>S/RES/2771(2025)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2093,57 +1957,53 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/607)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.11.json</t>
+          <t>A_80_607.json</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MONUSCO</t>
+          <t>UNFICYP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Add.11</t>
-        </is>
-      </c>
+          <t>United Nations Peacekeeping Force in Cyprus</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+          <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>The mandate of MONUSCO was established by the Security Council in its resolution 1925 (2010) and most recently extended by the Council until 20 December 2026 in its resolution 2808 (2025).</t>
+          <t>Pursuant to Security Council resolution 1325 (2000) and all subsequent resolutions on women and peace and security, UNFICYP will continue to support efforts for the full, meaningful and effective participation of women in peace and political processes and to bring together a broader range of women actors on both sides.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1925(2010)</t>
+          <t>https://docs.un.org/en/S/RES/1325(2000)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1925 (2010)</t>
+          <t>1325 (2000)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>S/RES/1925(2010)</t>
+          <t>S/RES/1325(2000)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2155,305 +2015,285 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/607)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.11.json</t>
+          <t>A_80_607.json</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MONUSCO</t>
+          <t>UNFICYP</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Add.11</t>
-        </is>
-      </c>
+          <t>United Nations Peacekeeping Force in Cyprus</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+          <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The mandate of MONUSCO was established by the Security Council in its resolution 1925 (2010) and most recently extended by the Council until 20 December 2026 in its resolution 2808 (2025).</t>
+          <t>The Force and the Department of Operational Support conducted a civilian staffing review in the 2024/25 period pursuant to General Assembly resolution 76/274.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
+          <t>https://docs.un.org/en/A/RES/76/274</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2808 (2025)</t>
+          <t>76/274</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>S/RES/2808(2025)</t>
+          <t>A/RES/76/274</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.11.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MONUSCO</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Add.11</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>By the same resolution, the Mission has been authorized to support the implementation of a permanent ceasefire in line with resolution 2773 (2025).</t>
+          <t>The Regional Service Centre in Entebbe, Uganda (RSCE), was established in July 2010, by the General Assembly in its resolution 64/269, as a shared service centre for missions in the region under the global field support strategy.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2773(2025)</t>
+          <t>https://docs.un.org/en/A/RES/64/269</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2773 (2025)</t>
+          <t>64/269</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>S/RES/2773(2025)</t>
+          <t>A/RES/64/269</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.11.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MONUSCO</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Add.11</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Under Security Council resolution 2808 (2025), MONUSCO is authorized to support the implementation of a permanent ceasefire, including through participation in the Ceasefire Oversight and Verification Mechanism and the provision of technical and logistical assistance to the Expanded Joint Verification Mechanism Plus.</t>
+          <t>In its resolution 69/307, the General Assembly decided to give RSCE operational and managerial independence and requested that the Secretary-General submit a budget proposal for the Centre for the period from 1 July 2016 to 30 June 2017, to be charged against the client missions.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
+          <t>https://docs.un.org/en/A/RES/69/307</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2808 (2025)</t>
+          <t>69/307</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>S/RES/2808(2025)</t>
+          <t>A/RES/69/307</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.11.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MONUSCO</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Add.11</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The Advisory Committee notes that paragraph 53 of Security Council resolution 2808 (2025) requested the Secretary-General to report to the Council by 1 March 2026 with progress towards the establishment and operationalization of the Ceasefire Oversight and Verification Mechanism, as well as realistic, concrete, cost effective and operational proposals on how MONUSCO could further support the implementation of a permanent ceasefire, especially in the hotspot areas of North and South Kivu, while also indicating that the Council intends to consider, in a later resolution and taking into account proposals by the Secretary-General and the evolving situation on the ground, any necessary adjustments to the mandate of MONUSCO.</t>
+          <t>The Centre’s mandate was expanded to provide additional services to other entities, as well as to develop broader cooperation with regional organizations, such as the African Union, following the adoption by the General Assembly of its resolution 78/294.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
+          <t>https://docs.un.org/en/A/RES/78/294</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2808 (2025)</t>
+          <t>78/294</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>S/RES/2808(2025)</t>
+          <t>A/RES/78/294</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.12.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Add.12</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>The mandate of UNIFIL was established by the Security Council in its resolutions 425 (1978) and 426 (1978) and was most recently extended by the Council in its resolution 2790 (2025), by which it extended the mandate for a final time until 31 December 2026, when the Force is to cease its operations and to start from this date and within one year complete its orderly and safe drawdown and withdrawal of personnel (A/80/634, para.</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/425(1978)</t>
+          <t>https://docs.un.org/en/S/RES/2713(2023)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>425 (1978)</t>
+          <t>Panel of Experts pursuant to resolution 2713 (2023)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>S/RES/425(1978)</t>
+          <t>S/RES/2713(2023)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2465,57 +2305,53 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.12.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Add.12</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>The mandate of UNIFIL was established by the Security Council in its resolutions 425 (1978) and 426 (1978) and was most recently extended by the Council in its resolution 2790 (2025), by which it extended the mandate for a final time until 31 December 2026, when the Force is to cease its operations and to start from this date and within one year complete its orderly and safe drawdown and withdrawal of personnel (A/80/634, para.</t>
+          <t>The Centre made a smooth transition to supporting the United Nations Transitional Assistance Mission in Somalia after the United Nations Assistance Mission in Somalia ended its operations on 31 October 2024 pursuant to Security Council resolution 2753 (2024).</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/426(1978)</t>
+          <t>https://docs.un.org/en/S/RES/2753(2024)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>426 (1978)</t>
+          <t>2753 (2024)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>S/RES/426(1978)</t>
+          <t>S/RES/2753(2024)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2527,181 +2363,169 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.12.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Add.12</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>The mandate of UNIFIL was established by the Security Council in its resolutions 425 (1978) and 426 (1978) and was most recently extended by the Council in its resolution 2790 (2025), by which it extended the mandate for a final time until 31 December 2026, when the Force is to cease its operations and to start from this date and within one year complete its orderly and safe drawdown and withdrawal of personnel (A/80/634, para.</t>
+          <t>The budgets of tenant units were transferred to their parent offices under the support account, effective from the 2025/26 period, as approved by the General Assembly in its resolution 79/300.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+          <t>https://docs.un.org/en/A/RES/79/300</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2790 (2025)</t>
+          <t>79/300</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>S/RES/2790(2025)</t>
+          <t>A/RES/79/300</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.12.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Add.12</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>The Secretary-General indicates that UNIFIL will, during the first six months of the 2026/27 period, prioritize activities aimed at supporting the parties in maintaining the cessation of hostilities and stability along the Blue Line, recommitting to the full implementation of Security Council resolution 1701 (2006) and taking concrete steps towards addressing outstanding provisions of the resolution, including steps towards a permanent ceasefire, and a long-term political solution between Lebanon and Israel.</t>
+          <t>15) and endorsed by the General Assembly in its resolution 77/306, are presented in table 2.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+          <t>https://docs.un.org/en/A/RES/77/306</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1701 (2006)</t>
+          <t>77/306</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>S/RES/1701(2006)</t>
+          <t>A/RES/77/306</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.12.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Add.12</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>UNIFIL will also support relevant enhanced diplomatic efforts to resolve any dispute or reservations pertaining to the international border between Lebanon and Israel, pursuant to resolution 2790 (2025) (ibid.</t>
+          <t>Effective 1 July 2026, RSCE will assume responsibility for the provision of residual liquidation support to the United Nations Investigative Team to Promote Accountability for Crimes Committed by Da’esh/Islamic State in Iraq and the Levant, whose mandate was terminated by the Security Council in its resolution 2697 (2023), as from 17 September 2024, and the United Nations Assistance Mission for Iraq (UNAMI), whose mandate was terminated by the Council, in its resolution 2732 (2024), as from 31 December 2025.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2697(2023)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2790 (2025)</t>
+          <t>2697 (2023)</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>S/RES/2790(2025)</t>
+          <t>S/RES/2697(2023)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2713,57 +2537,53 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.12.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Add.12</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>This configuration reflects the mission closure plan, the drawdown sequencing, activities mandated by Security Council resolution 2790 (2025) (paras.</t>
+          <t>Effective 1 July 2026, RSCE will assume responsibility for the provision of residual liquidation support to the United Nations Investigative Team to Promote Accountability for Crimes Committed by Da’esh/Islamic State in Iraq and the Levant, whose mandate was terminated by the Security Council in its resolution 2697 (2023), as from 17 September 2024, and the United Nations Assistance Mission for Iraq (UNAMI), whose mandate was terminated by the Council, in its resolution 2732 (2024), as from 31 December 2025.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2732(2024)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2790 (2025)</t>
+          <t>2732 (2024)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>S/RES/2790(2025)</t>
+          <t>S/RES/2732(2024)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2775,305 +2595,285 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.12.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Add.12</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>The Advisory Committee was also informed that, pursuant to the request contained in Security Council resolution 2790 (2025) that the Secretary-General explore options for the future of the implementation of resolution 1701 (2006), by 1 June 2026, the Department of Political and Peacebuilding Affairs and the Department of Peace Operations were developing options, in consultation with Member States and relevant United Nations entities, for the consideration of the Secretary-General, who will share proposals with the Security Council no later than 1 June 2026.</t>
+          <t>32–39), the consolidation of payroll services was approved by the General Assembly in its resolution 80/242.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+          <t>https://docs.un.org/en/A/RES/80/242</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2790 (2025)</t>
+          <t>80/242</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>S/RES/2790(2025)</t>
+          <t>A/RES/80/242</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.12.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Add.12</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>The Advisory Committee was also informed that, pursuant to the request contained in Security Council resolution 2790 (2025) that the Secretary-General explore options for the future of the implementation of resolution 1701 (2006), by 1 June 2026, the Department of Political and Peacebuilding Affairs and the Department of Peace Operations were developing options, in consultation with Member States and relevant United Nations entities, for the consideration of the Secretary-General, who will share proposals with the Security Council no later than 1 June 2026.</t>
+          <t>Following the adoption by the General Assembly of its resolution 78/294, RSCE will lead the consolidation of administrative and financial services, excluding payroll, for 16 active clients of the Kuwait Joint Support Office.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+          <t>https://docs.un.org/en/A/RES/78/294</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>1701 (2006)</t>
+          <t>78/294</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>S/RES/1701(2006)</t>
+          <t>A/RES/78/294</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.12.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Add.12</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Taken together, these measures are intended to ensure an orderly and safe drawdown and withdrawal in accordance with Security Council resolution 2790 (2025).</t>
+          <t>In line with General Assembly resolutions 70/286 and 76/274, RSCE has continued to advance the nationalization of posts, supporting the professional growth of the local workforce and strengthening long-term sustainability.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+          <t>https://docs.un.org/en/A/RES/70/286</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2790 (2025)</t>
+          <t>70/286</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>S/RES/2790(2025)</t>
+          <t>A/RES/70/286</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.12.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Add.12</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The Advisory Committee notes that proposed reductions for UNIFIL are related to the implementation of Security Council resolution 2790 (2025) and the mandate for an orderly and safe drawdown and withdrawal of personnel starting in January 2027.</t>
+          <t>In line with General Assembly resolutions 70/286 and 76/274, RSCE has continued to advance the nationalization of posts, supporting the professional growth of the local workforce and strengthening long-term sustainability.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+          <t>https://docs.un.org/en/A/RES/76/274</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2790 (2025)</t>
+          <t>76/274</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>S/RES/2790(2025)</t>
+          <t>A/RES/76/274</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.13.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>UNMISS</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>United Nations Mission in South Sudan</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Add.13</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Mission in South Sudan</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>The mandate of UNMISS was established by the Security Council in its resolution 1996 (2011) and was most recently extended until 30 April 2026 in resolution 2779 (2025).</t>
+          <t>International</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1996(2011)</t>
+          <t>https://docs.un.org/en/S/RES/2713(2023)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1996 (2011)</t>
+          <t>Panel of Experts pursuant to resolution 2713 (2023)</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>S/RES/1996(2011)</t>
+          <t>S/RES/2713(2023)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3085,57 +2885,53 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.13.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>UNMISS</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>United Nations Mission in South Sudan</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Add.13</t>
-        </is>
-      </c>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Mission in South Sudan</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Mandate and planning assumptions</t>
+          <t>Mandate, results achieved and planned outcome</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>The mandate of UNMISS was established by the Security Council in its resolution 1996 (2011) and was most recently extended until 30 April 2026 in resolution 2779 (2025).</t>
+          <t>National</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2779(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2713(2023)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2779 (2025)</t>
+          <t>Panel of Experts pursuant to resolution 2713 (2023)</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>S/RES/2779(2025)</t>
+          <t>S/RES/2713(2023)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3147,60 +2943,4058 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/604)</t>
+          <t>PKM 26/27 (A/80/611)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A_80_604_ADD.13.json</t>
+          <t>A_80_611.json</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>RSCE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Uniformed</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2713(2023)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Panel of Experts pursuant to resolution 2713 (2023)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>S/RES/2713(2023)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/614)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>A_80_614.json</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UNISFA</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>The mandate of the United Nations Interim Security Force for Abyei (UNISFA) was established by the Security Council in its resolution 1990 (2011) and extended in subsequent resolutions.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1990(2011)</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>1990 (2011)</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>S/RES/1990(2011)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/614)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A_80_614.json</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>UNISFA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided by the Council in its resolutions 2708 (2023) and 2760 (2024).</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2708(2023)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2708 (2023)</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>S/RES/2708(2023)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/614)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A_80_614.json</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UNISFA</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided by the Council in its resolutions 2708 (2023) and 2760 (2024).</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2760(2024)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2760 (2024)</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>S/RES/2760(2024)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/614)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A_80_614.json</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>UNISFA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2802 (2025), by which it extended the mandate until 15 November 2026.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2802(2025)</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2802 (2025)</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>S/RES/2802(2025)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/614)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>A_80_614.json</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>UNISFA</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>In accordance with Security Council resolution 2802 (2025), by which the Council extended the Force’s mandate until 15 November 2026, UNISFA will prepare an additional report for the Council on security situation activities undertaken by authorities in the Sudan and South Sudan to assess demonstrable progress towards achieving benchmarks outlined by the Council, and it will provide a comprehensive assessment of the security implications of any potential drawdown.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2802(2025)</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2802 (2025)</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>S/RES/2802(2025)</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/614)</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>A_80_614.json</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>UNISFA</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>During the first half of the 2025/26 period, a civilian staffing review was conducted by UNISFA and the Department of Operational Support, in accordance with paragraph 28 of General Assembly resolution 76/274.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/76/274</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>76/274</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>A/RES/76/274</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>General Assembly resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/615)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>A_80_615.json</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>UNMIK</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>United Nations Interim Administration Mission in Kosovo</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Interim Administration Mission in Kosovo</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>The mandate of UNMIK was established by the Security Council in its resolution 1244 (1999).</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1244(1999)</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>1244 (1999)</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>S/RES/1244(1999)</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/615)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>A_80_615.json</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>UNMIK</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>United Nations Interim Administration Mission in Kosovo</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Interim Administration Mission in Kosovo</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>In implementing those priorities, the Mission ensured the integration of gender and youth perspectives into all aspects of its work, in accordance with Security Council resolutions 1325 (2000) and 2250 (2015) and subsequent resolutions on women and peace and security and on youth, peace and security, respectively.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1325(2000)</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>1325 (2000)</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>S/RES/1325(2000)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/615)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>A_80_615.json</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>UNMIK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>United Nations Interim Administration Mission in Kosovo</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Interim Administration Mission in Kosovo</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>In implementing those priorities, the Mission ensured the integration of gender and youth perspectives into all aspects of its work, in accordance with Security Council resolutions 1325 (2000) and 2250 (2015) and subsequent resolutions on women and peace and security and on youth, peace and security, respectively.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2250(2015)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2250 (2015)</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>S/RES/2250(2015)</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/615)</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>A_80_615.json</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>UNMIK</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>United Nations Interim Administration Mission in Kosovo</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Interim Administration Mission in Kosovo</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>During the 2025/26 period, a civilian staffing review of UNMIK was undertaken in line with General Assembly resolution 76/274.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/76/274</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>76/274</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>A/RES/76/274</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>General Assembly resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/621)</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>A_80_621.json</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
           <t>UNMISS</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>United Nations Mission in South Sudan</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Add.13</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Financing of the United Nations Mission in South Sudan</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Mandate and planning assumptions</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>The Security Council, in its resolution 2779 (2025), mandated UNMISS to use its good offices and provide appropriate technical assistance and advice to the Revitalized Transitional Government of National Unity and relevant stakeholders, based on realistic planning assumptions and clear timelines.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>The mandate of United Nations Mission in South Sudan (UNMISS) was established by the Security Council in its resolution 1996 (2011).</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1996(2011)</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>1996 (2011)</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>S/RES/1996(2011)</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/621)</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>A_80_621.json</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>UNMISS</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided in its resolutions 2729 (2024), 2778 (2025) and 2779 (2025).</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2729(2024)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2729 (2024)</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>S/RES/2729(2024)</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/621)</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>A_80_621.json</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>UNMISS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided in its resolutions 2729 (2024), 2778 (2025) and 2779 (2025).</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2778(2025)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2778 (2025)</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>S/RES/2778(2025)</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/621)</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>A_80_621.json</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>UNMISS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided in its resolutions 2729 (2024), 2778 (2025) and 2779 (2025).</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
         <is>
           <t>https://docs.un.org/en/S/RES/2779(2025)</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>2779 (2025)</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>S/RES/2779(2025)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/621)</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>A_80_621.json</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>UNMISS</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>During the 2025/26 period, the Mission conducted a civilian staffing review, in accordance with paragraph 28 of General Assembly resolution 76/274.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/76/274</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>76/274</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>A/RES/76/274</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>General Assembly resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/621)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>A_80_621.json</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>UNMISS</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>In line with the request from the General Assembly in its resolution 76/274 for further nationalization and taking into account both the capacity of national staff and the potential for increased efficiencies, the civilian staffing review recommended six nationalizations through the conversion of posts and positions.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/76/274</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>76/274</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>A/RES/76/274</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>General Assembly resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/623)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>A_80_623.json</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>MINUSCA</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>The mandate of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic (MINUSCA) was established by the Security Council in its resolution 2149 (2014).</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2149(2014)</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2149 (2014)</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>S/RES/2149(2014)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/623)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>A_80_623.json</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>MINUSCA</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided in its resolutions 2709 (2023) and 2759 (2024).</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2709(2023)</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2709 (2023)</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>S/RES/2709(2023)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/623)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>A_80_623.json</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MINUSCA</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided in its resolutions 2709 (2023) and 2759 (2024).</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2759(2024)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2759 (2024)</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>S/RES/2759(2024)</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/623)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>A_80_623.json</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MINUSCA</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2800 (2025), by which the Council extended the mandate until 15 November 2026.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2800(2025)</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2800 (2025)</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>S/RES/2800(2025)</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/623)</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>A_80_623.json</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MINUSCA</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>In its resolution 2800 (2025), the Security Council reduced the authorized strength of the uniformed component of the Mission by deciding that MINUSCA shall comprise up to 14,046 military personnel, including 580 military observers and military staff officers, and 2,999 police personnel, including 589 individual police officers and 2,410 formed police unit personnel, as well as 108 corrections officers, recalled its intention to keep that number under continuous review, taking into account progress on the security situation and the objective of transition and eventual drawdown of MINUSCA when conditions were met, and further expressed its firm intention to review the number of personnel following the successful completion of the electoral process scheduled in 2025 and 2026.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2800(2025)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2800 (2025)</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>S/RES/2800(2025)</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/623)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>A_80_623.json</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MINUSCA</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>The successful conduct of the combined presidential, legislative, regional and municipal elections on 28 December 2025 marked a significant milestone for the Central African Republic and provides an opportunity for MINUSCA to adjust its footprint and posture in line with its mandate under Security Council resolution 2800 (2025).</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2800(2025)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2800 (2025)</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>S/RES/2800(2025)</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/623)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>A_80_623.json</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MINUSCA</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>In the light of the post-election context, and in preparation for implementation of the MINUSCA mandate during the 2026/27 period, the Mission is initiating a phase of consolidation, reconfiguration and internal strategic review, in line with paragraph 48 of Security Council resolution 2800 (2025).</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2800(2025)</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2800 (2025)</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>S/RES/2800(2025)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/623)</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>A_80_623.json</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MINUSCA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>In line with the request from the General Assembly in its resolution 76/274 for further nationalization and taking into account the proposed abolishment of one post of Senior Victims’ Rights Officer (P-5) in the Office of the Special Representative of the Secretary-General, the capacity of national staff and the potential for increased efficiencies, it is proposed that one post of Victims’ Rights Officer (National Professional Officer) be established.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/76/274</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>76/274</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>A/RES/76/274</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>General Assembly resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>The mandate of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo (MONUSCO) was established by the Security Council in its resolution 1925 (2010).</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1925(2010)</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>1925 (2010)</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>S/RES/1925(2010)</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided in its resolutions 2717 (2023) and 2765 (2024).</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2717(2023)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2717 (2023)</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>S/RES/2717(2023)</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided in its resolutions 2717 (2023) and 2765 (2024).</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2765(2024)</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2765 (2024)</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>S/RES/2765(2024)</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2808 (2025), by which it extended the mandate until 20 December 2026.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2808 (2025)</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>In the 2026/27 period, the strategic priorities of MONUSCO are expected to contribute to (a) the protection of civilians in its areas of deployment; (b) the achievement of the objectives set out in Security Council resolution 2773 (2025); and (c) support for the stabilization and strengthening of State institutions in the Democratic Republic of the Congo.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2773(2025)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2773 (2025)</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>S/RES/2773(2025)</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>In addition to its continuing support for regional and international peace efforts, under Council resolution 2808 (2025) the Mission was formally authorized to support the implementation of a permanent ceasefire.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2808 (2025)</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Under Security Council resolution 2808 (2025), MONUSCO is authorized to support the implementation of a permanent ceasefire, including through participation in the Ceasefire Oversight and Verification Mechanism and the provision of technical and logistical support to the Expanded Joint Verification Mechanism Plus.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2808 (2025)</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>MONUSCO will, to the extent possible, leverage existing infrastructure, assets and support arrangements in North Kivu and Ituri, while retaining an ability to scale, reconfigure or redeploy to support ceasefire monitoring and verification activities in South Kivu, as explicitly authorized in resolution 2808 (2025).</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2808 (2025)</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>The Mission will sustain its logistical support for the forward force headquarters in Beni to facilitate joint operations and strengthened coordination with FARDC, while remaining agile and flexible to expand its areas of support to South Kivu, pursuant to Security Council resolution 2808 (2025).</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2808 (2025)</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Subsequently, the Security Council, in its resolution 2808 (2025), introduced a new mandate priority for MONUSCO to support the implementation of Council resolution 2773 (2025), with a focus on support for a permanent ceasefire.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2808 (2025)</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>S/RES/2808(2025)</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/624)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>A_80_624.json</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MONUSCO</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Subsequently, the Security Council, in its resolution 2808 (2025), introduced a new mandate priority for MONUSCO to support the implementation of Council resolution 2773 (2025), with a focus on support for a permanent ceasefire.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2773(2025)</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2773 (2025)</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>S/RES/2773(2025)</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/628)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>A_80_628.json</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>UNSOS</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>The United Nations Support Office in Somalia (UNSOS) was established by the Security Council in its resolution 1863 (2009) to provide support to the African Union Mission in Somalia.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1863(2009)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>1863 (2009)</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>S/RES/1863(2009)</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/628)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>A_80_628.json</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>UNSOS</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided in its resolutions 2748 (2024), 2767 (2024) and 2776 (2025).</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2748(2024)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2748 (2024)</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>S/RES/2748(2024)</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/628)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>A_80_628.json</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>UNSOS</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided in its resolutions 2748 (2024), 2767 (2024) and 2776 (2025).</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2767(2024)</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2767 (2024)</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>S/RES/2767(2024)</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/628)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>A_80_628.json</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>UNSOS</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided in its resolutions 2748 (2024), 2767 (2024) and 2776 (2025).</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2776(2025)</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2776 (2025)</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>S/RES/2776(2025)</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/628)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>A_80_628.json</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>UNSOS</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2809 (2025), by which it extended the mandate until 31 December 2026.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2809(2025)</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2809 (2025)</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>S/RES/2809(2025)</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/628)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>A_80_628.json</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>UNSOS</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>The Council, in its resolution 2809 (2025), also reaffirmed the continued role of UNSOS in providing required logistical and administrative services, including to the United Nations Transitional Assistance Mission in Somalia (UNTMIS) on a cost-recovery basis until the conclusion of its phased drawdown by 31 October 2026.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2809(2025)</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2809 (2025)</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>S/RES/2809(2025)</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/628)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>A_80_628.json</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>UNSOS</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>In this context, and consistent with paragraph 23 of resolution 2809 (2025), UNSOS will continue to adapt its support for AUSSOM, taking into account measures implemented to manage its liquidity shortfall and prioritizing the sustained capacity of AUSSOM to consolidate peace and security gains across phases 2, 3 and 4 of the concept of operations.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2809(2025)</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2809 (2025)</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>S/RES/2809(2025)</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/628)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>A_80_628.json</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>UNSOS</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>In its resolution 2753 (2024), the Security Council expressed its intention to terminate the mandate of UNTMIS at the end of the anticipated two-phased transition on 31 October 2026.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2753(2024)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2753 (2024)</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>S/RES/2753(2024)</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/628)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>A_80_628.json</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>UNSOS</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Pursuant to resolution 2809 (2025), the implementation of the human rights due diligence policy remains mandatory for all United Nations support provided to AUSSOM and Somali security forces.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2809(2025)</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2809 (2025)</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>S/RES/2809(2025)</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/628)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>A_80_628.json</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>UNSOS</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>These positions had been dedicated to providing administrative and operational support to UNTMIS on a cost-recovery basis in accordance with Security Council resolution 2767 (2024).</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2767(2024)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2767 (2024)</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>S/RES/2767(2024)</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/630)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>A_80_630.json</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>UNSOH</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Mandate and planned outcome</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>The mandate of UNSOH was established by the Security Council in its resolution 2793 (2025).</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2793 (2025)</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>S/RES/2793(2025)</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/630)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>A_80_630.json</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>UNSOH</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Mandate and planned outcome</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>In the resolution, the Council authorized Member States to transition the Multinational Security Support Mission, as authorized in resolution 2699 (2023) and renewed in resolution 2751 (2024), to the Gang Suppression Force, in close cooperation and coordination with the Government of Haiti, for an initial period of 12 months, comprising an authorized personnel ceiling of 5,550 for the Gang Suppression Force, consisting of 5,500 uniformed personnel, comprising both military and police personnel, and 50 civilians.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2699(2023)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2699 (2023)</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>S/RES/2699(2023)</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/630)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>A_80_630.json</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>UNSOH</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Mandate and planned outcome</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>In the resolution, the Council authorized Member States to transition the Multinational Security Support Mission, as authorized in resolution 2699 (2023) and renewed in resolution 2751 (2024), to the Gang Suppression Force, in close cooperation and coordination with the Government of Haiti, for an initial period of 12 months, comprising an authorized personnel ceiling of 5,550 for the Gang Suppression Force, consisting of 5,500 uniformed personnel, comprising both military and police personnel, and 50 civilians.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2751(2024)</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2751 (2024)</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>S/RES/2751(2024)</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/630)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>A_80_630.json</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>UNSOH</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Mandate and planned outcome</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>The Security Council noted the assessment by the Secretary-General, contained in his letter to the President of the Security Council (S/2025/122), that a United Nations support office should provide comprehensive logistical and operational support to the Gang Suppression Force and, owing to the unique character of the Force, requested the Secretary-General to establish the United Nations Support Office in Haiti (UNSOH) to provide support, primarily to the Gang Suppression Force, the United Nations Integrated Office in Haiti (BINUH), the Haitian National Police and the Haitian Armed Forces on any joint operations with the Gang Suppression Force, as well as technical support to the Organization of American States (OAS), with a view to assuming full logistical support responsibility for the Gang Suppression Force within six months of the adoption of resolution 2793 (2025).</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2793 (2025)</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>S/RES/2793(2025)</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/630)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>A_80_630.json</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>UNSOH</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Mandate and planned outcome</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>UNSOH will provide, on a cost-recovery basis, the standard range of mission support services to BINUH in support of the delivery of its mandate, as extended in resolution 2814 (2026), with a view to assuming full responsibility by 1 February 2026.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2814(2026)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2814 (2026)</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>S/RES/2814(2026)</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/630)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>A_80_630.json</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>UNSOH</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Mandate and planned outcome</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Through its resolution 2793 (2025), the Security Council established UNSOH as a separate entity in Haiti, with dedicated leadership.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2793 (2025)</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>S/RES/2793(2025)</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/630)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>A_80_630.json</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>UNSOH</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Mandate and planned outcome</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>The requirements take into account the milestones outlined in resolution 2793 (2025), including the provision of support to Gang Suppression Force starting on 1 April 2026 and the anticipated deployment of the Force.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2793 (2025)</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>S/RES/2793(2025)</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>The mandate of the United Nations Interim Force in Lebanon (UNIFIL) was established by the Security Council in its resolutions 425 (1978) and 426 (1978), expanded in its resolution 1701 (2006) and extended in subsequent resolutions.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/425(1978)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>425 (1978)</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>S/RES/425(1978)</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>The mandate of the United Nations Interim Force in Lebanon (UNIFIL) was established by the Security Council in its resolutions 425 (1978) and 426 (1978), expanded in its resolution 1701 (2006) and extended in subsequent resolutions.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/426(1978)</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>426 (1978)</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>S/RES/426(1978)</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>The mandate of the United Nations Interim Force in Lebanon (UNIFIL) was established by the Security Council in its resolutions 425 (1978) and 426 (1978), expanded in its resolution 1701 (2006) and extended in subsequent resolutions.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>1701 (2006)</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided by the Council in its resolutions 2695 (2023) and 2749 (2024).</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2695(2023)</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2695 (2023)</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>S/RES/2695(2023)</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>The mandate for the performance period was provided by the Council in its resolutions 2695 (2023) and 2749 (2024).</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2749(2024)</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2749 (2024)</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>S/RES/2749(2024)</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2790 (2025), by which it extended the mandate for a final time until 31 December 2026, when the Force is to cease its operations and to start from this date and within one year its orderly and safe drawdown and withdrawal of personnel.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>The subsequent announcement of a cessation of hostilities between Lebanon and Israel (see S/2024/870), effective 27 November 2024, created a period of new opportunities for the implementation of resolution 1701 (2006), with the parties committing to its full implementation.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>1701 (2006)</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Until 27 November 2024, with the movement of UNIFIL highly restricted, the Force’s operational priorities were monitoring violations of resolution 1701 (2006), with significantly increased reporting requirements, as well as liaison and coordination between the parties.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>1701 (2006)</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>UNIFIL finalized its adaptation plan in January 2025 and subsequently implemented a more robust, operations-centred modus operandi, with dedicated operations involving multiple military assets, focused on assisting the Lebanese Armed Forces in deploying south of the Litani River, creating a safe and secure environment and preventing violations of resolution 1701 (2006).</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>1701 (2006)</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>UNIFIL will, during the first six months of the 2026/27 period, prioritize activities aimed at supporting the parties in maintaining the cessation of hostilities and stability along the Blue Line, recommitting to the full implementation of resolution 1701 (2006) and taking concrete steps towards addressing outstanding provisions of that resolution, including steps towards a permanent ceasefire, and a long-term political solution between Lebanon and Israel, which are key to long-term stability.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>1701 (2006)</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Pursuant to resolution 2790 (2025), UNIFIL will also remain ready to support, when relevant, enhanced diplomatic efforts to resolve any dispute or reservations pertaining to the international border between Lebanon and Israel.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>UNIFIL will continue to monitor, investigate and report on violations of resolution 1701 (2006), concurrently supporting the parties in fulfilling their commitments to the resolution.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>1701 (2006)</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>UNIFIL will cooperate with and support the mechanism set out in resolution 2790 (2025), including through the Force’s monitoring and verification role.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>UNIFIL will intensify its support to the Lebanese Armed Forces to ensure their effective and sustainable deployment south of the Litani River and to enhance their capacities to implement Security Council resolution 1701 (2006).</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>1701 (2006)</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>A lean and essential leadership and coordination structure of the executive direction and management component will continue to provide unified oversight, ensuring that political, operational and administrative activities remain fully aligned with Security Council resolution 2790 (2025), the directives of the Secretary-General and the relevant policies of the Organization.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Strategic communications will continue to manage the Force’s public narrative and legacy messaging, countering disinformation and misinformation and ensuring transparent engagement with host authorities and the public, including as provided for under Council resolution 2790 (2025).</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/634)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>A_80_634.json</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Mandate, results achieved and planned outcome</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>All parties will remain committed to the implementation of Security Council resolution 1701 (2006); UNIFIL will be afforded freedom of movement by all parties</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>All parties will remain committed to the implementation of Security Council resolution 1701 (2006)</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
         <is>
           <t>Security Council resolutions</t>
         </is>

--- a/data/processed/pkm2026/all_mandates.xlsx
+++ b/data/processed/pkm2026/all_mandates.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L34"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,12 +481,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/596)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A_80_596.json</t>
+          <t>A_80_604_ADD.1.json</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -499,7 +499,11 @@
           <t>United Nations Disengagement Observer Force</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Add.1</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Disengagement Observer Force</t>
@@ -507,12 +511,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>The mandate of the United Nations Disengagement Observer Force (UNDOF) was established by the Security Council in its resolution 350 (1974).</t>
+          <t>The mandate of UNDOF was established by the Security Council in its resolution 350 (1974) and was renewed most recently in its resolution 2811 (2025), by which it was extended until 30 June 2026.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -539,12 +543,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/596)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>A_80_596.json</t>
+          <t>A_80_604_ADD.1.json</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -557,7 +561,11 @@
           <t>United Nations Disengagement Observer Force</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Add.1</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Disengagement Observer Force</t>
@@ -565,12 +573,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2811 (2025), by which it extended the Force's mandate until 30 June 2026.</t>
+          <t>The mandate of UNDOF was established by the Security Council in its resolution 350 (1974) and was renewed most recently in its resolution 2811 (2025), by which it was extended until 30 June 2026.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -597,12 +605,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/607)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A_80_607.json</t>
+          <t>A_80_604_ADD.2.json</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -615,7 +623,11 @@
           <t>United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Add.2</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
@@ -623,12 +635,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>The mandate of UNFICYP was established by the Security Council in its resolution 186 (1964).</t>
+          <t>UNFICYP was established by the Security Council in its resolution 186 (1964), and its mandate was extended most recently, until 31 January 2027, pursuant to resolution 2815 (2026).</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -655,12 +667,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/607)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A_80_607.json</t>
+          <t>A_80_604_ADD.2.json</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -673,7 +685,11 @@
           <t>United Nations Peacekeeping Force in Cyprus</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Add.2</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>Financing of the United Nations Peacekeeping Force in Cyprus</t>
@@ -681,12 +697,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2815 (2026), by which it extended the mandate until 31 January 2027.</t>
+          <t>UNFICYP was established by the Security Council in its resolution 186 (1964), and its mandate was extended most recently, until 31 January 2027, pursuant to resolution 2815 (2026).</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -713,53 +729,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/634)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A_80_634.json</t>
+          <t>A_80_604_ADD.3.json</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>MINURSO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>United Nations Mission for the Referendum in Western Sahara</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Add.3</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>The mandate of the United Nations Interim Force in Lebanon (UNIFIL) was established by the Security Council in its resolutions 425 (1978) and 426 (1978).</t>
+          <t>The mandate of MINURSO was established by the Security Council in its resolution 690 (1991) and extended most recently, until 31 October 2026, in its resolution 2797 (2025).</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/425(1978)</t>
+          <t>https://docs.un.org/en/S/RES/690(1991)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>425 (1978)</t>
+          <t>690 (1991)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>S/RES/425(1978)</t>
+          <t>S/RES/690(1991)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -771,53 +791,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/634)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A_80_634.json</t>
+          <t>A_80_604_ADD.3.json</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>MINURSO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
+          <t>United Nations Mission for the Referendum in Western Sahara</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Add.3</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The mandate of the United Nations Interim Force in Lebanon (UNIFIL) was established by the Security Council in its resolutions 425 (1978) and 426 (1978).</t>
+          <t>The mandate of MINURSO was established by the Security Council in its resolution 690 (1991) and extended most recently, until 31 October 2026, in its resolution 2797 (2025).</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/426(1978)</t>
+          <t>https://docs.un.org/en/S/RES/2797(2025)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>426 (1978)</t>
+          <t>2797 (2025)</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>S/RES/426(1978)</t>
+          <t>S/RES/2797(2025)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -829,28 +853,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/634)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A_80_634.json</t>
+          <t>A_80_604_ADD.4.json</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Add.4</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -860,55 +888,59 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>The mandate was expanded by the Security Council in its resolution 1701 (2006).</t>
+          <t>The Regional Service Centre in Entebbe was established in July 2010, following the adoption by the General Assembly of its resolution 64/269, as a shared service centre for missions in the region under the global field support strategy.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+          <t>https://docs.un.org/en/A/RES/64/269</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1701 (2006)</t>
+          <t>64/269</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>S/RES/1701(2006)</t>
+          <t>A/RES/64/269</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/634)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A_80_634.json</t>
+          <t>A_80_604_ADD.4.json</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>UNIFIL</t>
+          <t>RSCE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>United Nations Interim Force in Lebanon</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Regional Service Centre in Entebbe</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Add.4</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -918,80 +950,84 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2790 (2025), by which it extended the mandate for a final time until 31 December 2026.</t>
+          <t>By its resolution 78/294, the Assembly expanded the mandate of RSCE to provide additional services to other entities, including the African Union.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+          <t>https://docs.un.org/en/A/RES/78/294</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2790 (2025)</t>
+          <t>78/294</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>S/RES/2790(2025)</t>
+          <t>A/RES/78/294</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Security Council resolutions</t>
+          <t>General Assembly resolutions</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/614)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A_80_614.json</t>
+          <t>A_80_604_ADD.6.json</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UNISFA</t>
+          <t>UNMIK</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>United Nations Interim Security Force for Abyei</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>United Nations Interim Administration Mission in Kosovo</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Add.6</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Interim Security Force for Abyei</t>
+          <t>Financing of the United Nations Interim Administration Mission in Kosovo</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>The mandate of UNISFA was established by the Security Council in its resolution 1990 (2011).</t>
+          <t>The mandate of UNMIK was established by the Security Council in its resolution 1244 (1999).</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1990(2011)</t>
+          <t>https://docs.un.org/en/S/RES/1244(1999)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1990 (2011)</t>
+          <t>1244 (1999)</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>S/RES/1990(2011)</t>
+          <t>S/RES/1244(1999)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1003,53 +1039,57 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/614)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A_80_614.json</t>
+          <t>A_80_604_ADD.7.json</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UNISFA</t>
+          <t>UNSOS</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>United Nations Interim Security Force for Abyei</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Add.7</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Interim Security Force for Abyei</t>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2802 (2025), by which it extended the mandate until 15 November 2026.</t>
+          <t>The mandate of UNSOS was established by the Security Council in resolution 1863 (2009) and was most recently extended until 31 December 2026 in Council resolution 2809 (2025).</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2802(2025)</t>
+          <t>https://docs.un.org/en/S/RES/1863(2009)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2802 (2025)</t>
+          <t>1863 (2009)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>S/RES/2802(2025)</t>
+          <t>S/RES/1863(2009)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1061,53 +1101,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/615)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A_80_615.json</t>
+          <t>A_80_604_ADD.7.json</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>UNMIK</t>
+          <t>UNSOS</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>United Nations Interim Administration Mission in Kosovo</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Add.7</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Interim Administration Mission in Kosovo</t>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>The mandate of UNMIK was established by the Security Council in its resolution 1244 (1999).</t>
+          <t>The mandate of UNSOS was established by the Security Council in resolution 1863 (2009) and was most recently extended until 31 December 2026 in Council resolution 2809 (2025).</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1244(1999)</t>
+          <t>https://docs.un.org/en/S/RES/2809(2025)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1244 (1999)</t>
+          <t>2809 (2025)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>S/RES/1244(1999)</t>
+          <t>S/RES/2809(2025)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1119,12 +1163,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/628)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A_80_628.json</t>
+          <t>A_80_604_ADD.7.json</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1137,7 +1181,11 @@
           <t>United Nations Support Office in Somalia</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Add.7</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
@@ -1145,27 +1193,27 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>UNSOS was established by the Security Council in its resolution 1863 (2009) to provide support to the African Union Mission in Somalia.</t>
+          <t>For the 2026/27 period, UNSOS support will continue to be aligned with the phased implementation of the AUSSOM strategic concept of operations (2024) (see Security Council resolution 2767 (2024)).</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1863(2009)</t>
+          <t>https://docs.un.org/en/S/RES/2767(2024)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1863 (2009)</t>
+          <t>2767 (2024)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>S/RES/1863(2009)</t>
+          <t>S/RES/2767(2024)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1177,12 +1225,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/628)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A_80_628.json</t>
+          <t>A_80_604_ADD.7.json</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1195,7 +1243,11 @@
           <t>United Nations Support Office in Somalia</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Add.7</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
@@ -1203,27 +1255,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>The United Nations Guard Unit was authorized by the Security Council in its resolution 2124 (2013).</t>
+          <t>The Advisory Committee notes that phase 1 of the approved concept of operations planned for the realignment of troops and the transfer of locations to Somali security forces and recalls that the budget for UNSOS for 2024/25 was proposed and approved on the basis of 10,626 ATMIS personnel, in accordance with Security Council resolution 2710 (2023), but 12,626 were retained throughout the same period, pursuant to resolution 2741 (2024).</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2124(2013)</t>
+          <t>https://docs.un.org/en/S/RES/2710(2023)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2124 (2013)</t>
+          <t>2710 (2023)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>S/RES/2124(2013)</t>
+          <t>S/RES/2710(2023)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1235,12 +1287,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/628)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>A_80_628.json</t>
+          <t>A_80_604_ADD.7.json</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1253,7 +1305,11 @@
           <t>United Nations Support Office in Somalia</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Add.7</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
@@ -1261,27 +1317,27 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2809 (2025), by which it extended the mandate until 31 December 2026.</t>
+          <t>The Advisory Committee notes that phase 1 of the approved concept of operations planned for the realignment of troops and the transfer of locations to Somali security forces and recalls that the budget for UNSOS for 2024/25 was proposed and approved on the basis of 10,626 ATMIS personnel, in accordance with Security Council resolution 2710 (2023), but 12,626 were retained throughout the same period, pursuant to resolution 2741 (2024).</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2809(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2741(2024)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2809 (2025)</t>
+          <t>2741 (2024)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>S/RES/2809(2025)</t>
+          <t>S/RES/2741(2024)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1293,53 +1349,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/630)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A_80_630.json</t>
+          <t>A_80_604_ADD.7.json</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>UNSOH</t>
+          <t>UNSOS</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Haiti</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Add.7</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Support Office in Haiti</t>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>The mandate of UNSOH was established by the Security Council in its resolution 2793 (2025).</t>
+          <t>Subsequently, in paragraph 21 of its resolution 2767 (2024), the Council adjusted the authorized ceiling to 11,826 uniformed personnel beginning from 1 July 2025, which resulted in movements of contingents during the current budget period, including the repatriation of one formed police unit and 470 defence forces personnel, together with associated contingent-owned equipment.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2767(2024)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2793 (2025)</t>
+          <t>2767 (2024)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>S/RES/2793(2025)</t>
+          <t>S/RES/2767(2024)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1351,53 +1411,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/630)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>A_80_630.json</t>
+          <t>A_80_604_ADD.7.json</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>UNSOH</t>
+          <t>UNSOS</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>United Nations Support Office in Haiti</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Add.7</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Support Office in Haiti</t>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>UNSOH will provide mission support services to BINUH in support of the delivery of its mandate, as extended in resolution 2814 (2026).</t>
+          <t>UNSOS will continue to provide mandated logistics support to the Somali security forces engaged in joint or coordinated operations with AUSSOM through the United Nations trust fund established by Security Council resolution 2124 (2013) (ibid.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2814(2026)</t>
+          <t>https://docs.un.org/en/S/RES/2124(2013)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2814 (2026)</t>
+          <t>2124 (2013)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>S/RES/2814(2026)</t>
+          <t>S/RES/2124(2013)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1409,53 +1473,57 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/624)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>A_80_624.json</t>
+          <t>A_80_604_ADD.7.json</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MONUSCO</t>
+          <t>UNSOS</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Add.7</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>The mandate of MONUSCO was established by the Security Council in its resolution 1925 (2010).</t>
+          <t>Following the anticipated closure of UNTMIS by 31 October 2026 in accordance with Security Council resolution 2753 (2024), UNSOS will implement the UNTMIS mission support transition plan, including the reduction of its physical footprint, environmental cleanup, asset disposal and administrative support (A/80/628, para.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1925(2010)</t>
+          <t>https://docs.un.org/en/S/RES/2753(2024)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1925 (2010)</t>
+          <t>2753 (2024)</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>S/RES/1925(2010)</t>
+          <t>S/RES/2753(2024)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1467,53 +1535,57 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/624)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>A_80_624.json</t>
+          <t>A_80_604_ADD.7.json</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MONUSCO</t>
+          <t>UNSOS</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Add.7</t>
+        </is>
+      </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>In the 2026/27 period, the strategic priorities of the Mission include the achievement of the objectives set out in Security Council resolution 2773 (2025).</t>
+          <t>UNSOS will also be responsible for the implementation of the human rights due diligence policy in Somalia, pursuant to Security Council resolution 2809 (2025), which has been conducted by UNTMIS to date (A/80/628, para.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2773(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2809(2025)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2773 (2025)</t>
+          <t>2809 (2025)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>S/RES/2773(2025)</t>
+          <t>S/RES/2809(2025)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1525,53 +1597,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/624)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>A_80_624.json</t>
+          <t>A_80_604_ADD.7.json</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MONUSCO</t>
+          <t>UNSOS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>United Nations Support Office in Somalia</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Add.7</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+          <t>Financing of the activities arising from Security Council resolution 1863 (2009)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2808 (2025), by which it extended the mandate until 20 December 2026.</t>
+          <t>Upon enquiry, the Advisory Committee was informed that the independent strategic review pursuant to Security Council resolution 2767 (2024), conducted in early 2025, identified structural efficiencies amounting to at least $43.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2767(2024)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2808 (2025)</t>
+          <t>2767 (2024)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>S/RES/2808(2025)</t>
+          <t>S/RES/2767(2024)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1583,53 +1659,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/623)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>A_80_623.json</t>
+          <t>A_80_604_ADD.8.json</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MINUSCA</t>
+          <t>UNSOH</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Add.8</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+          <t>Financing of the United Nations Support Office in Haiti</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>The mandate of MINUSCA was established by the Security Council in its resolution 2149 (2014).</t>
+          <t>The Security Council, by its resolution 2793 (2025) of 30 September 2025, acting under Chapter VII of the Charter of the United Nations, authorized Member States to transition the Multinational Security Support Mission to the Gang Suppression Force, with an authorized ceiling of 5,550 personnel (5,500 uniformed military and police personnel and 50 civilians).</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2149(2014)</t>
+          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2149 (2014)</t>
+          <t>2793 (2025)</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>S/RES/2149(2014)</t>
+          <t>S/RES/2793(2025)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1641,53 +1721,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/623)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>A_80_623.json</t>
+          <t>A_80_604_ADD.8.json</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MINUSCA</t>
+          <t>UNSOH</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Add.8</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+          <t>Financing of the United Nations Support Office in Haiti</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2800 (2025), by which it extended the mandate until 15 November 2026.</t>
+          <t>In its resolution 2793 (2025), the Security Council also indicates that the Standing Group of Partners for the Gang Suppression Force is responsible for the selection of the special representative for the Force, who was appointed in December 2025, to provide strategic representation and coordination and also of the Force Commander of the Force, to be responsible for operational command and day-to-day operational decision-making.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2800(2025)</t>
+          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2800 (2025)</t>
+          <t>2793 (2025)</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>S/RES/2800(2025)</t>
+          <t>S/RES/2793(2025)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1699,53 +1783,57 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/590)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>A_80_590.json</t>
+          <t>A_80_604_ADD.8.json</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MINUSMA</t>
+          <t>UNSOH</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>United Nations Support Office in Haiti</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Add.8</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
+          <t>Financing of the United Nations Support Office in Haiti</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Mandate performance</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>The mandate of MINUSMA was established by the Security Council in its resolution 2100 (2013).</t>
+          <t>In its resolution 2793 (2025), the Security Council requested the Secretary-General to ensure strong coordination and cooperation among all actors in the United Nations system in order to prevent duplication of effort and to maximize the leveraging of existing resources, and stressed that the Head of UNSOH should have separate quantifiable compacts with the Head of BINUH for the delivery of support to BINUH and with the special representative for the Gang Suppression Force.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2100(2013)</t>
+          <t>https://docs.un.org/en/S/RES/2793(2025)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2100 (2013)</t>
+          <t>2793 (2025)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>S/RES/2100(2013)</t>
+          <t>S/RES/2793(2025)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1757,53 +1845,57 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/590)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A_80_590.json</t>
+          <t>A_80_604_ADD.9.json</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MINUSMA</t>
+          <t>MINUSCA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Add.9</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in Mali</t>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Mandate performance</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>The Security Council, in paragraph 1 of resolution 2690 (2023), decided to terminate the mandate of MINUSMA as from 30 June 2023.</t>
+          <t>MINUSCA was established by the Security Council in its resolution 2149 (2014), and its mandate was most recently extended until 15 November 2026 in Council resolution 2800 (2025).</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2690(2023)</t>
+          <t>https://docs.un.org/en/S/RES/2149(2014)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2690 (2023)</t>
+          <t>2149 (2014)</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>S/RES/2690(2023)</t>
+          <t>S/RES/2149(2014)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1815,53 +1907,57 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/600)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>A_80_600.json</t>
+          <t>A_80_604_ADD.9.json</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MINURSO</t>
+          <t>MINUSCA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>United Nations Mission for the Referendum in Western Sahara</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
+          <t>United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Add.9</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
+          <t>Financing of the United Nations Multidimensional Integrated Stabilization Mission in the Central African Republic</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>The mandate of MINURSO was established by the Security Council in its resolution 690 (1991).</t>
+          <t>MINUSCA was established by the Security Council in its resolution 2149 (2014), and its mandate was most recently extended until 15 November 2026 in Council resolution 2800 (2025).</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/690(1991)</t>
+          <t>https://docs.un.org/en/S/RES/2800(2025)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>690 (1991)</t>
+          <t>2800 (2025)</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>S/RES/690(1991)</t>
+          <t>S/RES/2800(2025)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1873,53 +1969,57 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/600)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>A_80_600.json</t>
+          <t>A_80_604_ADD.10.json</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MINURSO</t>
+          <t>UNISFA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>United Nations Mission for the Referendum in Western Sahara</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
+          <t>United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Add.10</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Mission for the Referendum in Western Sahara</t>
+          <t>Financing of the United Nations Interim Security Force for Abyei</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2797 (2025), by which it extended the mandate until 31 October 2026.</t>
+          <t>The mandate of UNISFA was established by the Security Council in its resolution 1990 (2011) and most recently extended by the Council in its resolution 2802 (2025), until 15 November 2026.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2797(2025)</t>
+          <t>https://docs.un.org/en/S/RES/1990(2011)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2797 (2025)</t>
+          <t>1990 (2011)</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>S/RES/2797(2025)</t>
+          <t>S/RES/1990(2011)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1931,53 +2031,57 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/621)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>A_80_621.json</t>
+          <t>A_80_604_ADD.10.json</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>UNMISS</t>
+          <t>UNISFA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>United Nations Mission in South Sudan</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
+          <t>United Nations Interim Security Force for Abyei</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Add.10</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Mission in South Sudan</t>
+          <t>Financing of the United Nations Interim Security Force for Abyei</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>The mandate of UNMISS was established by the Security Council in its resolution 1996 (2011).</t>
+          <t>The mandate of UNISFA was established by the Security Council in its resolution 1990 (2011) and most recently extended by the Council in its resolution 2802 (2025), until 15 November 2026.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/1996(2011)</t>
+          <t>https://docs.un.org/en/S/RES/2802(2025)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1996 (2011)</t>
+          <t>2802 (2025)</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>S/RES/1996(2011)</t>
+          <t>S/RES/2802(2025)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -1989,53 +2093,57 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/621)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>A_80_621.json</t>
+          <t>A_80_604_ADD.11.json</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>UNMISS</t>
+          <t>MONUSCO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>United Nations Mission in South Sudan</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Add.11</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Mission in South Sudan</t>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>The most recent extension of the mandate was authorized by the Council in its resolution 2779 (2025), by which it extended the mandate until 30 April 2026.</t>
+          <t>The mandate of MONUSCO was established by the Security Council in its resolution 1925 (2010) and most recently extended by the Council until 20 December 2026 in its resolution 2808 (2025).</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/S/RES/2779(2025)</t>
+          <t>https://docs.un.org/en/S/RES/1925(2010)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2779 (2025)</t>
+          <t>1925 (2010)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>S/RES/2779(2025)</t>
+          <t>S/RES/1925(2010)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2047,346 +2155,1284 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/605)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>A_80_605.json</t>
+          <t>A_80_604_ADD.11.json</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>UNLB</t>
+          <t>MONUSCO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>United Nations Logistics Base at Brindisi</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Add.11</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Logistics Base at Brindisi</t>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>In its resolution 49/233 A of 23 December 1994, the General Assembly welcomed the establishment of the first permanent United Nations logistics base in Brindisi, Italy, to support peacekeeping operations.</t>
+          <t>The mandate of MONUSCO was established by the Security Council in its resolution 1925 (2010) and most recently extended by the Council until 20 December 2026 in its resolution 2808 (2025).</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/A/RES/49/233</t>
+          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>49/233</t>
+          <t>2808 (2025)</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>A/RES/49/233</t>
+          <t>S/RES/2808(2025)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>General Assembly resolutions</t>
+          <t>Security Council resolutions</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/605)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>A_80_605.json</t>
+          <t>A_80_604_ADD.11.json</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>UNLB</t>
+          <t>MONUSCO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>United Nations Logistics Base at Brindisi</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Add.11</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Logistics Base at Brindisi</t>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>In its resolution 63/262 of 24 December 2008, the General Assembly approved the establishment of site B, in Valencia, Spain, as a secondary active telecommunications and information technology facility.</t>
+          <t>By the same resolution, the Mission has been authorized to support the implementation of a permanent ceasefire in line with resolution 2773 (2025).</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/A/RES/63/262</t>
+          <t>https://docs.un.org/en/S/RES/2773(2025)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>63/262</t>
+          <t>2773 (2025)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>A/RES/63/262</t>
+          <t>S/RES/2773(2025)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>General Assembly resolutions</t>
+          <t>Security Council resolutions</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/605)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>A_80_605.json</t>
+          <t>A_80_604_ADD.11.json</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>UNLB</t>
+          <t>MONUSCO</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>United Nations Logistics Base at Brindisi</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Add.11</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Logistics Base at Brindisi</t>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>UNLB is mandated to serve all field missions, Secretariat entities, and United Nations system entities, pursuant to General Assembly resolution 72/266 B on shifting the management paradigm in the United Nations.</t>
+          <t>Under Security Council resolution 2808 (2025), MONUSCO is authorized to support the implementation of a permanent ceasefire, including through participation in the Ceasefire Oversight and Verification Mechanism and the provision of technical and logistical assistance to the Expanded Joint Verification Mechanism Plus.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/A/RES/72/266B</t>
+          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>72/266 B</t>
+          <t>2808 (2025)</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>A/RES/72/266B</t>
+          <t>S/RES/2808(2025)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>General Assembly resolutions</t>
+          <t>Security Council resolutions</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/605)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>A_80_605.json</t>
+          <t>A_80_604_ADD.11.json</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>UNLB</t>
+          <t>MONUSCO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>United Nations Logistics Base at Brindisi</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
+          <t>United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Add.11</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Financing of the United Nations Logistics Base at Brindisi</t>
+          <t>Financing of the United Nations Organization Stabilization Mission in the Democratic Republic of the Congo</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>The Advisory Committee's recommendations were endorsed by the General Assembly in its resolution 78/295.</t>
+          <t>The Advisory Committee notes that paragraph 53 of Security Council resolution 2808 (2025) requested the Secretary-General to report to the Council by 1 March 2026 with progress towards the establishment and operationalization of the Ceasefire Oversight and Verification Mechanism, as well as realistic, concrete, cost effective and operational proposals on how MONUSCO could further support the implementation of a permanent ceasefire, especially in the hotspot areas of North and South Kivu, while also indicating that the Council intends to consider, in a later resolution and taking into account proposals by the Secretary-General and the evolving situation on the ground, any necessary adjustments to the mandate of MONUSCO.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/A/RES/78/295</t>
+          <t>https://docs.un.org/en/S/RES/2808(2025)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>78/295</t>
+          <t>2808 (2025)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>A/RES/78/295</t>
+          <t>S/RES/2808(2025)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>General Assembly resolutions</t>
+          <t>Security Council resolutions</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/611)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>A_80_611.json</t>
+          <t>A_80_604_ADD.12.json</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RSCE</t>
+          <t>UNIFIL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Regional Service Centre in Entebbe</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Add.12</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Mandate and planning assumptions</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>The Regional Service Centre in Entebbe (RSCE) was established in July 2010, by the General Assembly in its resolution 64/269, as a shared service centre for missions in the region.</t>
+          <t>The mandate of UNIFIL was established by the Security Council in its resolutions 425 (1978) and 426 (1978) and was most recently extended by the Council in its resolution 2790 (2025), by which it extended the mandate for a final time until 31 December 2026, when the Force is to cease its operations and to start from this date and within one year complete its orderly and safe drawdown and withdrawal of personnel (A/80/634, para.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://docs.un.org/en/A/RES/64/269</t>
+          <t>https://docs.un.org/en/S/RES/425(1978)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>64/269</t>
+          <t>425 (1978)</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>A/RES/64/269</t>
+          <t>S/RES/425(1978)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>General Assembly resolutions</t>
+          <t>Security Council resolutions</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PKM 26/27 (A/80/611)</t>
+          <t>PKM 26/27 (A/80/604)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>A_80_611.json</t>
+          <t>A_80_604_ADD.12.json</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>RSCE</t>
+          <t>UNIFIL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Regional Service Centre in Entebbe</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Add.12</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>The mandate of UNIFIL was established by the Security Council in its resolutions 425 (1978) and 426 (1978) and was most recently extended by the Council in its resolution 2790 (2025), by which it extended the mandate for a final time until 31 December 2026, when the Force is to cease its operations and to start from this date and within one year complete its orderly and safe drawdown and withdrawal of personnel (A/80/634, para.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/426(1978)</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>426 (1978)</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>S/RES/426(1978)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.12.json</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Add.12</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>The mandate of UNIFIL was established by the Security Council in its resolutions 425 (1978) and 426 (1978) and was most recently extended by the Council in its resolution 2790 (2025), by which it extended the mandate for a final time until 31 December 2026, when the Force is to cease its operations and to start from this date and within one year complete its orderly and safe drawdown and withdrawal of personnel (A/80/634, para.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.12.json</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Add.12</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>The Secretary-General indicates that UNIFIL will, during the first six months of the 2026/27 period, prioritize activities aimed at supporting the parties in maintaining the cessation of hostilities and stability along the Blue Line, recommitting to the full implementation of Security Council resolution 1701 (2006) and taking concrete steps towards addressing outstanding provisions of the resolution, including steps towards a permanent ceasefire, and a long-term political solution between Lebanon and Israel.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>1701 (2006)</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.12.json</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Add.12</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>UNIFIL will also support relevant enhanced diplomatic efforts to resolve any dispute or reservations pertaining to the international border between Lebanon and Israel, pursuant to resolution 2790 (2025) (ibid.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.12.json</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Add.12</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>This configuration reflects the mission closure plan, the drawdown sequencing, activities mandated by Security Council resolution 2790 (2025) (paras.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.12.json</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Add.12</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>The Advisory Committee was also informed that, pursuant to the request contained in Security Council resolution 2790 (2025) that the Secretary-General explore options for the future of the implementation of resolution 1701 (2006), by 1 June 2026, the Department of Political and Peacebuilding Affairs and the Department of Peace Operations were developing options, in consultation with Member States and relevant United Nations entities, for the consideration of the Secretary-General, who will share proposals with the Security Council no later than 1 June 2026.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.12.json</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Add.12</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>The Advisory Committee was also informed that, pursuant to the request contained in Security Council resolution 2790 (2025) that the Secretary-General explore options for the future of the implementation of resolution 1701 (2006), by 1 June 2026, the Department of Political and Peacebuilding Affairs and the Department of Peace Operations were developing options, in consultation with Member States and relevant United Nations entities, for the consideration of the Secretary-General, who will share proposals with the Security Council no later than 1 June 2026.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1701 (2006)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>S/RES/1701(2006)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.12.json</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Add.12</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Taken together, these measures are intended to ensure an orderly and safe drawdown and withdrawal in accordance with Security Council resolution 2790 (2025).</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.12.json</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>UNIFIL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Add.12</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations peacekeeping forces in the Middle East: United Nations Interim Force in Lebanon</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>The Advisory Committee notes that proposed reductions for UNIFIL are related to the implementation of Security Council resolution 2790 (2025) and the mandate for an orderly and safe drawdown and withdrawal of personnel starting in January 2027.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2790 (2025)</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>S/RES/2790(2025)</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.13.json</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>UNMISS</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Add.13</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>The mandate of UNMISS was established by the Security Council in its resolution 1996 (2011) and was most recently extended until 30 April 2026 in resolution 2779 (2025).</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/1996(2011)</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>1996 (2011)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>S/RES/1996(2011)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.13.json</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UNMISS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Add.13</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>The mandate of UNMISS was established by the Security Council in its resolution 1996 (2011) and was most recently extended until 30 April 2026 in resolution 2779 (2025).</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2779(2025)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2779 (2025)</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>S/RES/2779(2025)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/604)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>A_80_604_ADD.13.json</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>UNMISS</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Add.13</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Financing of the United Nations Mission in South Sudan</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Mandate and planning assumptions</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>The Security Council, in its resolution 2779 (2025), mandated UNMISS to use its good offices and provide appropriate technical assistance and advice to the Revitalized Transitional Government of National Unity and relevant stakeholders, based on realistic planning assumptions and clear timelines.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/S/RES/2779(2025)</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2779 (2025)</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>S/RES/2779(2025)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Security Council resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/605)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>A_80_605.json</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UNLB</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
           <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Mandate</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>The Centre's mandate was expanded to provide additional services to other entities, including the African Union, following the adoption by the General Assembly of its resolution 78/294.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>https://docs.un.org/en/A/RES/78/294</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>78/294</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>A/RES/78/294</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>In its resolution 49/233 A of 23 December 1994, the General Assembly welcomed the establishment of the first permanent United Nations logistics base in Brindisi, Italy, to support peacekeeping operations.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/49/233A</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>49/233 A</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>A/RES/49/233A</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>General Assembly resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/605)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>A_80_605.json</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>UNLB</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Mandate</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>In its resolution 63/262 of 24 December 2008, the General Assembly approved the establishment of site B, in Valencia, Spain, as a secondary active telecommunications and information technology facility.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/63/262</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>63/262</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>A/RES/63/262</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>General Assembly resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/605)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>A_80_605.json</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UNLB</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Mandate</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>UNLB is mandated to serve all field missions, Secretariat entities and United Nations system entities, pursuant to General Assembly resolution 72/266 B on shifting the management paradigm in the United Nations.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/72/266B</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>72/266 B</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>A/RES/72/266B</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>General Assembly resolutions</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PKM 26/27 (A/80/605)</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>A_80_605.json</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>UNLB</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>United Nations Logistics Base at Brindisi</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Administrative and budgetary aspects of the financing of the United Nations peacekeeping operations</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Mandate</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>In its resolution 78/295, the General Assembly endorsed the Advisory Committee's recommendations on the implementation of the management paradigm shift at UNLB.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>https://docs.un.org/en/A/RES/78/295</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>78/295</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>A/RES/78/295</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
         <is>
           <t>General Assembly resolutions</t>
         </is>

--- a/data/processed/pkm2026/all_mandates.xlsx
+++ b/data/processed/pkm2026/all_mandates.xlsx
@@ -3219,12 +3219,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UNLB</t>
+          <t>UNGSC Brindisi</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>United Nations Logistics Base at Brindisi</t>
+          <t>United Nations Logistics Base at Brindisi, Italy</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -3277,12 +3277,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>UNLB</t>
+          <t>UNGSC Brindisi</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>United Nations Logistics Base at Brindisi</t>
+          <t>United Nations Logistics Base at Brindisi, Italy</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -3335,12 +3335,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>UNLB</t>
+          <t>UNGSC Brindisi</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>United Nations Logistics Base at Brindisi</t>
+          <t>United Nations Logistics Base at Brindisi, Italy</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
@@ -3393,12 +3393,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>UNLB</t>
+          <t>UNGSC Brindisi</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>United Nations Logistics Base at Brindisi</t>
+          <t>United Nations Logistics Base at Brindisi, Italy</t>
         </is>
       </c>
       <c r="E49" t="inlineStr"/>
